--- a/stories/arbres/TREE-AUT-004.xlsx
+++ b/stories/arbres/TREE-AUT-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est sur le chemin de l'école, avec papa. Maman a mis un goûter dans le sac. Il y a des jouets. Après le jeu, on range. Papa dit : les jouets retournent dans la caisse. On range.</t>
+          <t>Inès est sur le chemin de l'école, avec papa. Maman a mis un goûter dans le sac. Il y a des jouets. Après le jeu, on range. Les jouets retournent dans la caisse. On range.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est sur le chemin de l'école, avec papa. Maman a mis un goûter dans le sac. Il y a des jouets. Après le jeu, on range.
+papa|Les jouets retournent dans la caisse. On range.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le chemin, il y a un petit bac à sable. Inès joue un peu. Puis elle range. Les jouets retournent dans la caisse. Papa tient la caisse. On entend un oiseau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Après le jeu, on range ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On range. On met dans la caisse. Inès respire. Papa est là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est rouge. Papa ferme le couvercle. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le bac à sable. Puis les cubes. Puis rouge. La couverture est douce. Inès sourit. Papa sourit aussi. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. Le savon sent bon. Inès prend la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Inès se souvient de le bac à sable. Et de les cubes. Et de vert. Un chat miaule une fois. Inès enfile ses chaussons. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3615,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est bleue. Papa ferme le couvercle. Papa dit : je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est bleue. Papa ferme le couvercle. Je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3753,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est bleue. Papa ferme le couvercle.
+papa|Je suis là. Après le jeu, on range.
+narrateur|Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3948,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4117,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Inès s'arrête. Un linge sèche à l'air. Inès souffle, puis sourit à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4284,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4451,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Inès range le livre. bleu reste près de le bac à sable. Une cloche tinte, tout loin. Inès répète tout bas le geste. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4618,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4647,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un ballon s'immobilise. Inès écoute papa encore une fois. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un ballon s'immobilise. Inès écoute papa encore une fois. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4785,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un ballon s'immobilise. Inès écoute papa encore une fois. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4952,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5119,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est verte. Papa ferme le couvercle. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5312,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5481,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint rouge. la dînette est rangé. le bac à sable est fini. Les chaussures font toc toc. Inès range encore un peu, près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5648,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5815,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Inès pose la dînette. le bac à sable est derrière. On souffle doucement. Inès ferme la porte, tout doux. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5982,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6149,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre vert. Papa a vu le bac à sable. Et la dînette. Une feuille tombe. Inès range la tasse. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6316,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6483,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le chemin, il y a un petit toboggan. Inès glisse une fois. Puis elle range. Les jouets retournent dans la caisse. Maman a mis la caisse dans le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6668,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les jouets vont où ? Dans la caisse.</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6841,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On range. On met dans la caisse. Inès retient le geste. Papa sourit. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7032,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6871,7 +7061,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est rouge. On range après le jeu. Papa dit : je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est rouge. On range après le jeu. Je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7009,6 +7199,13 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est rouge. On range après le jeu.
+papa|Je suis là. Après le jeu, on range.
+narrateur|Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7197,6 +7394,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7361,6 +7563,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le toboggan. Puis les cubes. Puis rouge. On rit un peu. Inès chuchote : c'est fini. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7730,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7897,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. Un galet est encore chaud. Inès dit merci à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8064,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8231,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Inès se souvient de le toboggan. Et de les cubes. Et de vert. On écoute jusqu'au bout. Maman n'est pas loin. Inès les rejoint. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8398,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8565,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8758,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8927,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Inès s'arrête. Le vent est doux. Inès serre la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9094,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9261,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Inès range le livre. bleu reste près de le toboggan. Une tasse cliquette. Inès boit une gorgée d'eau. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9428,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9195,7 +9457,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Inès pose le livre à sa place. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Inès pose le livre à sa place. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9333,6 +9595,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Inès pose le livre à sa place. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9762,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9929,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est verte. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9845,6 +10122,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10009,6 +10291,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint rouge. la dînette est rangé. le toboggan est fini. Ça sent le pain chaud. Inès marche près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10458,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10625,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Inès pose la dînette. le toboggan est derrière. Un panier est posé sur le banc. Inès s'assoit près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10792,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10959,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre vert. Papa a vu le toboggan. Et la dînette. Une chaussette est encore sablée. Inès plie un pull. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11126,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10843,7 +11155,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, il y a des balançoires. Inès s'assoit un moment. Puis elle range. Les jouets retournent dans la caisse. Papa dit : après le jeu, on range.</t>
+          <t>Sur le chemin, il y a des balançoires. Inès s'assoit un moment. Puis elle range. Les jouets retournent dans la caisse. Après le jeu, on range.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10981,6 +11293,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le chemin, il y a des balançoires. Inès s'assoit un moment. Puis elle range. Les jouets retournent dans la caisse.
+papa|Après le jeu, on range.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11161,6 +11479,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On met les jouets dans la caisse ?</t>
         </is>
       </c>
     </row>
@@ -11329,6 +11652,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On range. On met dans la caisse. Inès hoche la tête. On continue, avec papa. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11515,6 +11843,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11677,6 +12010,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est rouge. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11865,6 +12203,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12029,6 +12372,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi les balançoires. Puis les cubes. Puis rouge. Un vélo passe au loin. Inès pose sa tête un moment. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12191,6 +12539,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12353,6 +12706,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. On range un objet. Inès montre bleu à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12515,6 +12873,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12677,6 +13040,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Inès se souvient de les balançoires. Et de les cubes. Et de vert. On se tient la main. Inès range les balançoires dans sa tête, comme un souvenir. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12839,6 +13207,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13001,6 +13374,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13189,6 +13567,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13353,6 +13736,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Inès s'arrête. Un crochet tient bien le manteau. Inès raccroche un linge. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13515,6 +13903,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13677,6 +14070,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Inès range le livre. bleu reste près de les balançoires. On entend un oiseau. Inès caresse le doudou. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13839,6 +14237,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13863,7 +14266,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>vert est là. le livre aussi. les balançoires reste dans le souvenir. On dit merci. Inès dit : j'ai appris. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Vert est là. le livre aussi. les balançoires reste dans le souvenir. On dit merci. J'ai appris. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14001,6 +14404,13 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. On dit merci.
+enfant-f|J'ai appris. Après le jeu, on range.
+narrateur|Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14163,6 +14573,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14187,7 +14602,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est verte. On range après le jeu. Papa dit : je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est verte. On range après le jeu. Je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14325,6 +14740,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est verte. On range après le jeu.
+papa|Je suis là. Après le jeu, on range.
+narrateur|Les jouets retournent dans la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14513,6 +14935,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14677,6 +15104,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Inès essuie ses mains. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14839,6 +15271,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15001,6 +15438,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de bleu. Inès pose la dînette. les balançoires est derrière. Le sol est un peu froid. Inès ferme le sac. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15163,6 +15605,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15325,6 +15772,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Inès montre vert. Papa a vu les balançoires. Et la dînette. Un ruban reste dans la poche. Inès tend vert à maman. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15487,6 +15939,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15505,7 +15962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15578,6 +16035,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-004.xlsx
+++ b/stories/arbres/TREE-AUT-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|Les jouets retournent dans la caisse. On range.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Sur le chemin, il y a un petit bac à sable. Inès joue un peu. Puis elle range. Les jouets retournent dans la caisse. Papa tient la caisse. On entend un oiseau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Après le jeu, on range ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. On range. On met dans la caisse. Inès respire. Papa est là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est rouge. Papa ferme le couvercle. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Inès a choisi le bac à sable. Puis les cubes. Puis rouge. La couverture est douce. Inès sourit. Papa sourit aussi. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. Le savon sent bon. Inès prend la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Inès se souvient de le bac à sable. Et de les cubes. Et de vert. Un chat miaule une fois. Inès enfile ses chaussons. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3760,6 +3779,7 @@
 narrateur|Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3955,6 +3975,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4122,6 +4143,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Inès s'arrête. Un linge sèche à l'air. Inès souffle, puis sourit à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4289,6 +4311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4456,6 +4479,7 @@
           <t>narrateur|Inès range le livre. bleu reste près de le bac à sable. Une cloche tinte, tout loin. Inès répète tout bas le geste. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4623,6 +4647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4790,6 +4815,7 @@
           <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un ballon s'immobilise. Inès écoute papa encore une fois. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4957,6 +4983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5151,7 @@
           <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est verte. Papa ferme le couvercle. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5319,6 +5347,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5486,6 +5515,7 @@
           <t>narrateur|Inès rejoint rouge. la dînette est rangé. le bac à sable est fini. Les chaussures font toc toc. Inès range encore un peu, près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5653,6 +5683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5820,6 +5851,7 @@
           <t>narrateur|Près de bleu. Inès pose la dînette. le bac à sable est derrière. On souffle doucement. Inès ferme la porte, tout doux. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5987,6 +6019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6154,6 +6187,7 @@
           <t>narrateur|Inès montre vert. Papa a vu le bac à sable. Et la dînette. Une feuille tombe. Inès range la tasse. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6321,6 +6355,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6488,6 +6523,7 @@
           <t>narrateur|Sur le chemin, il y a un petit toboggan. Inès glisse une fois. Puis elle range. Les jouets retournent dans la caisse. Maman a mis la caisse dans le sac.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6675,6 +6711,7 @@
           <t>narrateur|Les jouets vont où ? Dans la caisse.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6846,6 +6883,7 @@
           <t>narrateur|Oui. On range. On met dans la caisse. Inès retient le geste. Papa sourit. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7037,6 +7075,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7206,6 +7245,7 @@
 narrateur|Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7401,6 +7441,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7568,6 +7609,7 @@
           <t>narrateur|Inès a choisi le toboggan. Puis les cubes. Puis rouge. On rit un peu. Inès chuchote : c'est fini. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7735,6 +7777,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7902,6 +7945,7 @@
           <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. Un galet est encore chaud. Inès dit merci à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8069,6 +8113,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8236,6 +8281,7 @@
           <t>narrateur|Inès se souvient de le toboggan. Et de les cubes. Et de vert. On écoute jusqu'au bout. Maman n'est pas loin. Inès les rejoint. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8403,6 +8449,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8570,6 +8617,7 @@
           <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8765,6 +8813,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8932,6 +8981,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Inès s'arrête. Le vent est doux. Inès serre la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9099,6 +9149,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9266,6 +9317,7 @@
           <t>narrateur|Inès range le livre. bleu reste près de le toboggan. Une tasse cliquette. Inès boit une gorgée d'eau. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9433,6 +9485,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9600,6 +9653,7 @@
           <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Inès pose le livre à sa place. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9767,6 +9821,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9934,6 +9989,7 @@
           <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est verte. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10129,6 +10185,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10296,6 +10353,7 @@
           <t>narrateur|Inès rejoint rouge. la dînette est rangé. le toboggan est fini. Ça sent le pain chaud. Inès marche près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10463,6 +10521,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10630,6 +10689,7 @@
           <t>narrateur|Près de bleu. Inès pose la dînette. le toboggan est derrière. Un panier est posé sur le banc. Inès s'assoit près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10797,6 +10857,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10964,6 +11025,7 @@
           <t>narrateur|Inès montre vert. Papa a vu le toboggan. Et la dînette. Une chaussette est encore sablée. Inès plie un pull. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11131,6 +11193,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11299,6 +11362,7 @@
 papa|Après le jeu, on range.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11486,6 +11550,7 @@
           <t>narrateur|On met les jouets dans la caisse ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11657,6 +11722,7 @@
           <t>narrateur|Oui. On range. On met dans la caisse. Inès hoche la tête. On continue, avec papa. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11848,6 +11914,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12015,6 +12082,7 @@
           <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est rouge. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12210,6 +12278,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12377,6 +12446,7 @@
           <t>narrateur|Inès a choisi les balançoires. Puis les cubes. Puis rouge. Un vélo passe au loin. Inès pose sa tête un moment. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12544,6 +12614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12711,6 +12782,7 @@
           <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. On range un objet. Inès montre bleu à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12878,6 +12950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13045,6 +13118,7 @@
           <t>narrateur|Inès se souvient de les balançoires. Et de les cubes. Et de vert. On se tient la main. Inès range les balançoires dans sa tête, comme un souvenir. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13212,6 +13286,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13379,6 +13454,7 @@
           <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13574,6 +13650,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13741,6 +13818,7 @@
           <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Inès s'arrête. Un crochet tient bien le manteau. Inès raccroche un linge. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13908,6 +13986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14075,6 +14154,7 @@
           <t>narrateur|Inès range le livre. bleu reste près de les balançoires. On entend un oiseau. Inès caresse le doudou. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14242,6 +14322,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14411,6 +14492,7 @@
 narrateur|Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14578,6 +14660,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14747,6 +14830,7 @@
 narrateur|Les jouets retournent dans la caisse.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14942,6 +15026,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15109,6 +15194,7 @@
           <t>narrateur|Inès rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Inès essuie ses mains. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15276,6 +15362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15443,6 +15530,7 @@
           <t>narrateur|Près de bleu. Inès pose la dînette. les balançoires est derrière. Le sol est un peu froid. Inès ferme le sac. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15610,6 +15698,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15777,6 +15866,7 @@
           <t>narrateur|Inès montre vert. Papa a vu les balançoires. Et la dînette. Un ruban reste dans la poche. Inès tend vert à maman. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15944,6 +16034,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15962,7 +16053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16042,6 +16133,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16056,7 +16161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16243,6 +16348,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-004.xlsx
+++ b/stories/arbres/TREE-AUT-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ranger après le jeu — sur le chemin de l'école</t>
+          <t>La caisse sur le chemin</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila marche vers l'école. Le pain sent bon. Un petit square attend. Elle joue un peu, puis range les jouets dans la caisse.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès est sur le chemin de l'école, avec papa. Maman a mis un goûter dans le sac. Il y a des jouets. Après le jeu, on range. Les jouets retournent dans la caisse. On range.</t>
+          <t>Le pain chaud sort de la boulangerie. Ça sent la croûte dorée, tout le long de la rue. Une flaque brille comme un petit miroir. Le sac de Mila tape doucement son dos. Toc toc. Un moineau picore une miette. J'ai mis le goûter dans le sac. Tu as tes chaussons de sport, Mila ? Oui, maman. On marche ensemble jusqu'à l'école. Papa tient une petite caisse par la poignée. Des jouets dorment dedans. En ce moment, ils suivent le trottoir mouillé. Juste après le pain, il y a un petit square. Le sable est encore frais. Le toboggan brille. Les balançoires bougent un tout petit peu. On peut jouer un peu, Mila. Après le jeu, les jouets retournent dans la caisse. D'accord, papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,8 +1337,26 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès est sur le chemin de l'école, avec papa. Maman a mis un goûter dans le sac. Il y a des jouets. Après le jeu, on range.
-papa|Les jouets retournent dans la caisse. On range.</t>
+          <t>narrateur|Le pain chaud sort de la boulangerie.
+narrateur|Ça sent la croûte dorée, tout le long de la rue.
+narrateur|Une flaque brille comme un petit miroir.
+narrateur|Le sac de Mila tape doucement son dos.
+narrateur|Toc toc.
+narrateur|Un moineau picore une miette.
+maman|J'ai mis le goûter dans le sac.
+maman|Tu as tes chaussons de sport, Mila ?
+enfant-f|Oui, maman.
+papa|On marche ensemble jusqu'à l'école.
+narrateur|Papa tient une petite caisse par la poignée.
+narrateur|Des jouets dorment dedans.
+narrateur|En ce moment, ils suivent le trottoir mouillé.
+narrateur|Juste après le pain, il y a un petit square.
+narrateur|Le sable est encore frais.
+narrateur|Le toboggan brille.
+narrateur|Les balançoires bougent un tout petit peu.
+papa|On peut jouer un peu, Mila.
+maman|Après le jeu, les jouets retournent dans la caisse.
+enfant-f|D'accord, papa.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1354,7 +1384,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Mila joue où, un petit moment ? Le bac à sable, le toboggan, ou les balançoires ? Tu choisis.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1548,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Mila joue où, un petit moment ?
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|Tu choisis.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1578,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, il y a un petit bac à sable. Inès joue un peu. Puis elle range. Les jouets retournent dans la caisse. Papa tient la caisse. On entend un oiseau.</t>
+          <t>Mila s'agenouille près du bac à sable. Le sable est frais, un peu humide. Il coule entre ses doigts. Chh. Papa pose la caisse à côté. Tu joues un peu. Après, on range. Oui. Dans la caisse. Mila fait un petit tas. Un cube dépasse déjà du sable. Bravo, Mila. Le sable reste dans le bac. Un oiseau crie au-dessus du square. Quand le jeu est fini, les jouets vont dans la caisse. Je range après.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,10 +1718,25 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sur le chemin, il y a un petit bac à sable. Inès joue un peu. Puis elle range. Les jouets retournent dans la caisse. Papa tient la caisse. On entend un oiseau.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila s'agenouille près du bac à sable.
+narrateur|Le sable est frais, un peu humide.
+narrateur|Il coule entre ses doigts. Chh.
+narrateur|Papa pose la caisse à côté.
+papa|Tu joues un peu. Après, on range.
+enfant-f|Oui. Dans la caisse.
+narrateur|Mila fait un petit tas.
+narrateur|Un cube dépasse déjà du sable.
+maman|Bravo, Mila. Le sable reste dans le bac.
+narrateur|Un oiseau crie au-dessus du square.
+papa|Quand le jeu est fini, les jouets vont dans la caisse.
+enfant-f|Je range après.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1898,7 +1945,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On range. On met dans la caisse. Inès respire. Papa est là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Oui. Mila a joué un peu. Elle souffle sur ses mains. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse. La caisse attend, ouverte. Tu as fini de jouer au sable ?</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2042,7 +2089,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On range. On met dans la caisse. Inès respire. Papa est là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Oui.
+narrateur|Mila a joué un peu.
+narrateur|Elle souffle sur ses mains.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.
+narrateur|La caisse attend, ouverte.
+papa|Tu as fini de jouer au sable ?</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2070,7 +2124,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Quel jouet Mila sort, près du bac ? Les cubes, le livre, ou la dînette ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2234,7 +2288,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Quel jouet Mila sort, près du bac ?
+maman|Les cubes, le livre, ou la dînette ?</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2262,7 +2317,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est rouge. Papa ferme le couvercle. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près du bac à sable. Le sable sent la terre fraîche. Les cubes sont un peu sablés. Les cubes, Mila. Après le jeu, dans la caisse. Clic. Clic. Mila empile deux cubes. Ça fait clic. Le jeu est fini, tout doux. Elle met les cubes dans la caisse, un par un. Mila secoue un peu ses mains. Le sable tombe. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2402,7 +2457,18 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est rouge. Papa ferme le couvercle. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près du bac à sable.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Les cubes sont un peu sablés.
+papa|Les cubes, Mila. Après le jeu, dans la caisse.
+enfant-f|Clic. Clic.
+narrateur|Mila empile deux cubes. Ça fait clic.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle met les cubes dans la caisse, un par un.
+narrateur|Mila secoue un peu ses mains. Le sable tombe.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2430,7 +2496,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2664,9 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2694,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi le bac à sable. Puis les cubes. Puis rouge. La couverture est douce. Inès sourit. Papa sourit aussi. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti les cubes. Maintenant, la caisse rouge. Un moineau reprend sa miette, plus loin. Mila voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Elle pousse le couvercle. Toc. Bravo, Mila. Les jouets sont dans la caisse. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,7 +2834,19 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi le bac à sable. Puis les cubes. Puis rouge. La couverture est douce. Inès sourit. Papa sourit aussi. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Un moineau reprend sa miette, plus loin.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met un cube dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Bravo, Mila. Les jouets sont dans la caisse.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2794,7 +2874,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Ils reprennent le trottoir mouillé. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3014,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Ils reprennent le trottoir mouillé.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3048,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Inès s'arrête près de bleu. les cubes est rangé. Le savon sent bon. Inès prend la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti les cubes. Maintenant, la caisse bleue. La flaque du trottoir tremble un peu. Mila voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Elle pousse le couvercle. Toc. Tu as rangé. C'est du bon travail. Dans la caisse. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,10 +3188,26 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. Le savon sent bon. Inès prend la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse bleue.
+narrateur|La flaque du trottoir tremble un peu.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met un cube dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Tu as rangé. C'est du bon travail.
+enfant-f|Dans la caisse.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3130,7 +3232,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le pain de la boulangerie sent encore. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3372,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le pain de la boulangerie sent encore.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3406,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Inès se souvient de le bac à sable. Et de les cubes. Et de vert. Un chat miaule une fois. Inès enfile ses chaussons. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti les cubes. Maintenant, la caisse verte. Le pain chaud sent encore, vers la rue. Mila voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Elle pousse le couvercle. Toc. Après le jeu, tu as rangé. Bravo. J'ai fermé le couvercle. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,7 +3546,19 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Inès se souvient de le bac à sable. Et de les cubes. Et de vert. Un chat miaule une fois. Inès enfile ses chaussons. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse verte.
+narrateur|Le pain chaud sent encore, vers la rue.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met un cube dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Après le jeu, tu as rangé. Bravo.
+enfant-f|J'ai fermé le couvercle.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3466,7 +3586,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'école montre son portail, tout loin. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3726,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'école montre son portail, tout loin.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3760,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est bleue. Papa ferme le couvercle. Je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près du bac à sable. Le sable sent la terre fraîche. Le livre a un grain de sable sur la couverture. Le livre, Mila. Après, il va dans la caisse. Je l'essuie un peu. Mila ouvre le livre. Une image de lune. Le jeu est fini, tout doux. Elle ferme le livre. Elle le pose dans la caisse. Mila secoue un peu ses mains. Le sable tombe. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,9 +3900,18 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est bleue. Papa ferme le couvercle.
-papa|Je suis là. Après le jeu, on range.
-narrateur|Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près du bac à sable.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Le livre a un grain de sable sur la couverture.
+maman|Le livre, Mila. Après, il va dans la caisse.
+enfant-f|Je l'essuie un peu.
+narrateur|Mila ouvre le livre. Une image de lune.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle ferme le livre. Elle le pose dans la caisse.
+narrateur|Mila secoue un peu ses mains. Le sable tombe.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3804,7 +3939,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3972,7 +4107,9 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4000,7 +4137,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de le bac à sable. Inès s'arrête. Un linge sèche à l'air. Inès souffle, puis sourit à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti le livre. Maintenant, la caisse rouge. Un vélo passe. La cloche tinte une fois. Mila voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Elle pousse le couvercle. Toc. La caisse est fermée. Merci, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4140,7 +4277,19 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de le bac à sable. Inès s'arrête. Un linge sèche à l'air. Inès souffle, puis sourit à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Un vélo passe. La cloche tinte une fois.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met le livre dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+maman|La caisse est fermée. Merci, Mila.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4168,7 +4317,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La caisse tape un peu la jambe de papa. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4308,7 +4457,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La caisse tape un peu la jambe de papa.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4336,7 +4491,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Inès range le livre. bleu reste près de le bac à sable. Une cloche tinte, tout loin. Inès répète tout bas le geste. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti le livre. Maintenant, la caisse bleue. Le sac de Mila tape son dos. Toc. Mila voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Elle pousse le couvercle. Toc. On peut marcher. La caisse vient avec nous. Merci, papa. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4476,10 +4631,26 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Inès range le livre. bleu reste près de le bac à sable. Une cloche tinte, tout loin. Inès répète tout bas le geste. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse bleue.
+narrateur|Le sac de Mila tape son dos. Toc.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met le livre dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+papa|On peut marcher. La caisse vient avec nous.
+enfant-f|Merci, papa.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4504,7 +4675,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila marche sur les dalles, une par une. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4644,7 +4815,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila marche sur les dalles, une par une.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4672,7 +4849,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un ballon s'immobilise. Inès écoute papa encore une fois. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti le livre. Maintenant, la caisse verte. Le couvercle de la caisse attend. Mila voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Elle pousse le couvercle. Toc. Tu as mis les jouets dans la caisse. Merci, maman. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4812,7 +4989,19 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. le bac à sable reste dans le souvenir. Un ballon s'immobilise. Inès écoute papa encore une fois. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse verte.
+narrateur|Le couvercle de la caisse attend.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met le livre dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Tu as mis les jouets dans la caisse.
+enfant-f|Merci, maman.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4840,7 +5029,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une flaque reflète le sac. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4980,7 +5169,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une flaque reflète le sac.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5008,7 +5203,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est verte. Papa ferme le couvercle. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près du bac à sable. Le sable sent la terre fraîche. La dînette est froide, posée sur le bois du bac. La dînette, Mila. Après, dans la caisse. La tasse est petite. Mila pose une tasse sur une soucoupe. Ça cliquette. Le jeu est fini, tout doux. Elle range la dînette dans la caisse, tout doux. Mila secoue un peu ses mains. Le sable tombe. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5148,7 +5343,18 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Inès a joué avec les cubes. Elle range. Les cubes retournent dans la caisse. La caisse est verte. Papa ferme le couvercle. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près du bac à sable.
+narrateur|Le sable sent la terre fraîche.
+narrateur|La dînette est froide, posée sur le bois du bac.
+papa|La dînette, Mila. Après, dans la caisse.
+enfant-f|La tasse est petite.
+narrateur|Mila pose une tasse sur une soucoupe. Ça cliquette.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle range la dînette dans la caisse, tout doux.
+narrateur|Mila secoue un peu ses mains. Le sable tombe.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5176,7 +5382,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5344,7 +5550,9 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5372,7 +5580,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint rouge. la dînette est rangé. le bac à sable est fini. Les chaussures font toc toc. Inès range encore un peu, près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti la dînette. Maintenant, la caisse rouge. Une feuille tourne dans le bac. Mila voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Elle pousse le couvercle. Toc. Bravo. Le square est calme. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5512,7 +5720,19 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint rouge. la dînette est rangé. le bac à sable est fini. Les chaussures font toc toc. Inès range encore un peu, près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Une feuille tourne dans le bac.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met la tasse dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Bravo. Le square est calme.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5540,7 +5760,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le moineau n'est plus là. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5680,7 +5900,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le moineau n'est plus là.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5708,7 +5934,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Inès pose la dînette. le bac à sable est derrière. On souffle doucement. Inès ferme la porte, tout doux. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti la dînette. Maintenant, la caisse bleue. Le toboggan ne brille plus autant. Mila voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Elle pousse le couvercle. Toc. Tu as fini de ranger tes jouets ? Le livre est dedans. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5848,10 +6074,26 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Inès pose la dînette. le bac à sable est derrière. On souffle doucement. Inès ferme la porte, tout doux. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse bleue.
+narrateur|Le toboggan ne brille plus autant.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met la tasse dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Tu as fini de ranger tes jouets ?
+enfant-f|Le livre est dedans.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5876,7 +6118,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le square reste derrière, calme. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6016,7 +6258,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le square reste derrière, calme.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6044,7 +6292,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Inès montre vert. Papa a vu le bac à sable. Et la dînette. Une feuille tombe. Inès range la tasse. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du bac à sable. Elle a sorti la dînette. Maintenant, la caisse verte. La balançoire s'arrête, tout à fait. Mila voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Elle pousse le couvercle. Toc. Oui. C'est rangé. On y va. La tasse aussi. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6184,7 +6432,19 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Inès montre vert. Papa a vu le bac à sable. Et la dînette. Une feuille tombe. Inès range la tasse. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du bac à sable.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse verte.
+narrateur|La balançoire s'arrête, tout à fait.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met la tasse dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Oui. C'est rangé. On y va.
+enfant-f|La tasse aussi.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6212,7 +6472,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le goûter fait un petit bruit. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6352,7 +6612,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le goûter fait un petit bruit.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6380,7 +6646,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, il y a un petit toboggan. Inès glisse une fois. Puis elle range. Les jouets retournent dans la caisse. Maman a mis la caisse dans le sac.</t>
+          <t>Mila monte les deux marches du toboggan. Le métal est frais sous ses mains. Elle glisse une fois. Wouh. Ses pieds retrouvent le tapis souple. Une fois, Mila. Puis on range. Encore les pieds par terre. Bravo. Tu es descendue doucement. Papa garde la caisse près du pied du toboggan. Un jouet dépasse déjà. Après le jeu, les jouets retournent dans la caisse. Je range, papa.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6520,10 +6786,24 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sur le chemin, il y a un petit toboggan. Inès glisse une fois. Puis elle range. Les jouets retournent dans la caisse. Maman a mis la caisse dans le sac.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Mila monte les deux marches du toboggan.
+narrateur|Le métal est frais sous ses mains.
+narrateur|Elle glisse une fois. Wouh.
+narrateur|Ses pieds retrouvent le tapis souple.
+papa|Une fois, Mila. Puis on range.
+enfant-f|Encore les pieds par terre.
+maman|Bravo. Tu es descendue doucement.
+narrateur|Papa garde la caisse près du pied du toboggan.
+narrateur|Un jouet dépasse déjà.
+papa|Après le jeu, les jouets retournent dans la caisse.
+enfant-f|Je range, papa.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6548,7 +6828,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Les jouets vont où ? Dans la caisse.</t>
+          <t>Les jouets vont où ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6708,7 +6988,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Les jouets vont où ? Dans la caisse.</t>
+          <t>narrateur|Les jouets vont où ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6736,7 +7016,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On range. On met dans la caisse. Inès retient le geste. Papa sourit. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Oui. Les jouets vont dans la caisse. Mila le répète tout bas. Bravo. Dans la caisse. Après le jeu, on range. Dans la caisse, maman. Mila essuie ses mains sur son manteau. Tu as fini de glisser ?</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6880,7 +7160,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On range. On met dans la caisse. Inès retient le geste. Papa sourit. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Oui.
+narrateur|Les jouets vont dans la caisse.
+narrateur|Mila le répète tout bas.
+papa|Bravo. Dans la caisse.
+maman|Après le jeu, on range.
+enfant-f|Dans la caisse, maman.
+narrateur|Mila essuie ses mains sur son manteau.
+papa|Tu as fini de glisser ?</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6908,7 +7195,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Quel jouet Mila sort, près du toboggan ? Les cubes, le livre, ou la dînette ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7072,7 +7359,8 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Quel jouet Mila sort, près du toboggan ?
+papa|Les cubes, le livre, ou la dînette ?</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7100,7 +7388,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est rouge. On range après le jeu. Je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près du toboggan. Le métal du toboggan est encore frais. Les cubes attendent au pied du toboggan. Les cubes, Mila. Puis on range dans la caisse. Je fais une tour basse. Mila empile deux cubes. Ça fait clic. Le jeu est fini, tout doux. Elle met les cubes dans la caisse, un par un. Mila pose un pied sur le tapis souple. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7240,9 +7528,18 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est rouge. On range après le jeu.
-papa|Je suis là. Après le jeu, on range.
-narrateur|Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près du toboggan.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Les cubes attendent au pied du toboggan.
+maman|Les cubes, Mila. Puis on range dans la caisse.
+enfant-f|Je fais une tour basse.
+narrateur|Mila empile deux cubes. Ça fait clic.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle met les cubes dans la caisse, un par un.
+narrateur|Mila pose un pied sur le tapis souple.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7270,7 +7567,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7438,7 +7735,9 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7466,7 +7765,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi le toboggan. Puis les cubes. Puis rouge. On rit un peu. Inès chuchote : c'est fini. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti les cubes. Maintenant, la caisse rouge. Le goûter fait un petit bruit dans le sac. Mila voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Elle pousse le couvercle. Toc. Bravo, Mila. C'est du bon travail. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7606,7 +7905,19 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi le toboggan. Puis les cubes. Puis rouge. On rit un peu. Inès chuchote : c'est fini. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Le goûter fait un petit bruit dans le sac.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met un cube dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Bravo, Mila. C'est du bon travail.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7634,7 +7945,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila serre la main de maman. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7774,7 +8085,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila serre la main de maman.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7802,7 +8119,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Inès s'arrête près de bleu. les cubes est rangé. Un galet est encore chaud. Inès dit merci à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti les cubes. Maintenant, la caisse bleue. Un galet est encore chaud de soleil. Mila voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Elle pousse le couvercle. Toc. Les cubes sont dans la caisse. C'est lourd un peu. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7942,10 +8259,26 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. Un galet est encore chaud. Inès dit merci à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse bleue.
+narrateur|Un galet est encore chaud de soleil.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met un cube dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Les cubes sont dans la caisse.
+enfant-f|C'est lourd un peu.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7970,7 +8303,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Papa change d'épaule, pour la caisse. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8110,7 +8443,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Papa change d'épaule, pour la caisse.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8138,7 +8477,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Inès se souvient de le toboggan. Et de les cubes. Et de vert. On écoute jusqu'au bout. Maman n'est pas loin. Inès les rejoint. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti les cubes. Maintenant, la caisse verte. L'herbe colle un peu aux chaussures. Mila voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Elle pousse le couvercle. Toc. Le livre est à sa place, dans la caisse. On va à l'école. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8278,7 +8617,19 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Inès se souvient de le toboggan. Et de les cubes. Et de vert. On écoute jusqu'au bout. Maman n'est pas loin. Inès les rejoint. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse verte.
+narrateur|L'herbe colle un peu aux chaussures.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met un cube dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Le livre est à sa place, dans la caisse.
+enfant-f|On va à l'école.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8306,7 +8657,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une cloche tinte, plus près. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8446,7 +8797,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une cloche tinte, plus près.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8474,7 +8831,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près du toboggan. Le métal du toboggan est encore frais. Le livre est dans le sac, tout près. Le livre, Mila. Après, il retourne dans la caisse. Je regarde une page. Mila ouvre le livre. Une image de lune. Le jeu est fini, tout doux. Elle ferme le livre. Elle le pose dans la caisse. Mila pose un pied sur le tapis souple. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8614,7 +8971,18 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près du toboggan.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Le livre est dans le sac, tout près.
+papa|Le livre, Mila. Après, il retourne dans la caisse.
+enfant-f|Je regarde une page.
+narrateur|Mila ouvre le livre. Une image de lune.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle ferme le livre. Elle le pose dans la caisse.
+narrateur|Mila pose un pied sur le tapis souple.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8642,7 +9010,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8810,7 +9178,9 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8838,7 +9208,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de le toboggan. Inès s'arrête. Le vent est doux. Inès serre la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti le livre. Maintenant, la caisse rouge. La poignée de la caisse est lisse. Mila voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Elle pousse le couvercle. Toc. La dînette ne cliquette plus. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8978,7 +9348,19 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de le toboggan. Inès s'arrête. Le vent est doux. Inès serre la main de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse rouge.
+narrateur|La poignée de la caisse est lisse.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met le livre dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+papa|La dînette ne cliquette plus.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9006,7 +9388,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les chaussures de Mila font toc toc. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9146,7 +9528,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Les chaussures de Mila font toc toc.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9174,7 +9562,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Inès range le livre. bleu reste près de le toboggan. Une tasse cliquette. Inès boit une gorgée d'eau. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti le livre. Maintenant, la caisse bleue. Maman ajuste l'écharpe de Mila. Mila voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Elle pousse le couvercle. Toc. Après le jeu, on range. Tu l'as fait. Le sable est resté. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9314,10 +9702,26 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Inès range le livre. bleu reste près de le toboggan. Une tasse cliquette. Inès boit une gorgée d'eau. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse bleue.
+narrateur|Maman ajuste l'écharpe de Mila.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met le livre dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Après le jeu, on range. Tu l'as fait.
+enfant-f|Le sable est resté.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9342,7 +9746,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le vent pousse une feuille sèche. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9482,7 +9886,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le vent pousse une feuille sèche.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9510,7 +9920,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Inès pose le livre à sa place. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti le livre. Maintenant, la caisse verte. Papa souffle dans ses mains. Mila voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Elle pousse le couvercle. Toc. Merci, Mila. On reprend le chemin. C'est fini, le jeu. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9650,7 +10060,19 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. le toboggan reste dans le souvenir. Il y a des miettes sur la table. Inès pose le livre à sa place. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse verte.
+narrateur|Papa souffle dans ses mains.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met le livre dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Merci, Mila. On reprend le chemin.
+enfant-f|C'est fini, le jeu.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9678,7 +10100,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le portail de l'école est jaune. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9818,7 +10240,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le portail de l'école est jaune.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9846,7 +10274,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est verte. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près du toboggan. Le métal du toboggan est encore frais. La dînette est dans la caisse, déjà à moitié. La dînette, Mila. Après le jeu, on range. Je sors la tasse. Mila pose une tasse sur une soucoupe. Ça cliquette. Le jeu est fini, tout doux. Elle range la dînette dans la caisse, tout doux. Mila pose un pied sur le tapis souple. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9986,7 +10414,18 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Inès a lu le livre. Elle range. Le livre retourne dans la caisse. La caisse est verte. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près du toboggan.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|La dînette est dans la caisse, déjà à moitié.
+maman|La dînette, Mila. Après le jeu, on range.
+enfant-f|Je sors la tasse.
+narrateur|Mila pose une tasse sur une soucoupe. Ça cliquette.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle range la dînette dans la caisse, tout doux.
+narrateur|Mila pose un pied sur le tapis souple.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10014,7 +10453,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10182,7 +10621,9 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10210,7 +10651,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint rouge. la dînette est rangé. le toboggan est fini. Ça sent le pain chaud. Inès marche près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti la dînette. Maintenant, la caisse rouge. Le square redevient calme. Mila voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Elle pousse le couvercle. Toc. Tu tiens bien le couvercle. Bravo. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10350,7 +10791,19 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint rouge. la dînette est rangé. le toboggan est fini. Ça sent le pain chaud. Inès marche près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Le square redevient calme.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met la tasse dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Tu tiens bien le couvercle. Bravo.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10378,7 +10831,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila sent le pain, une dernière fois. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10518,7 +10971,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila sent le pain, une dernière fois.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10546,7 +11005,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Inès pose la dînette. le toboggan est derrière. Un panier est posé sur le banc. Inès s'assoit près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti la dînette. Maintenant, la caisse bleue. Une cloche d'école tinte, tout loin. Mila voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Elle pousse le couvercle. Toc. La caisse est prête. Bravo. La caisse est bleue. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10686,10 +11145,26 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Inès pose la dînette. le toboggan est derrière. Un panier est posé sur le banc. Inès s'assoit près de papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse bleue.
+narrateur|Une cloche d'école tinte, tout loin.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met la tasse dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+papa|La caisse est prête. Bravo.
+enfant-f|La caisse est bleue.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10714,7 +11189,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La caisse ne s'ouvre plus. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10854,7 +11329,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La caisse ne s'ouvre plus.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10882,7 +11363,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Inès montre vert. Papa a vu le toboggan. Et la dînette. Une chaussette est encore sablée. Inès plie un pull. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près du toboggan. Elle a sorti la dînette. Maintenant, la caisse verte. Le sable ne coule plus. Mila voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Elle pousse le couvercle. Toc. On marche jusqu'à l'école. La caisse est verte. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11022,7 +11503,19 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Inès montre vert. Papa a vu le toboggan. Et la dînette. Une chaussette est encore sablée. Inès plie un pull. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près du toboggan.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse verte.
+narrateur|Le sable ne coule plus.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met la tasse dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+maman|On marche jusqu'à l'école.
+enfant-f|La caisse est verte.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11050,7 +11543,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le trottoir sèche par plaques. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11190,7 +11683,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le trottoir sèche par plaques.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11218,7 +11717,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, il y a des balançoires. Inès s'assoit un moment. Puis elle range. Les jouets retournent dans la caisse. Après le jeu, on range.</t>
+          <t>Mila s'assoit sur une balançoire. Le siège est un peu froid. Elle avance tout doux, puis s'arrête. Un petit moment, Mila. Puis on range. Je me tiens bien. Bravo. Tes mains tiennent la corde. La caisse est posée dans l'herbe. Un couvercle attend, ouvert. Après le jeu, les jouets retournent dans la caisse. Après, je range. Une feuille tourne sous la balançoire.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11358,11 +11857,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sur le chemin, il y a des balançoires. Inès s'assoit un moment. Puis elle range. Les jouets retournent dans la caisse.
-papa|Après le jeu, on range.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Mila s'assoit sur une balançoire.
+narrateur|Le siège est un peu froid.
+narrateur|Elle avance tout doux, puis s'arrête.
+maman|Un petit moment, Mila. Puis on range.
+enfant-f|Je me tiens bien.
+papa|Bravo. Tes mains tiennent la corde.
+narrateur|La caisse est posée dans l'herbe.
+narrateur|Un couvercle attend, ouvert.
+maman|Après le jeu, les jouets retournent dans la caisse.
+enfant-f|Après, je range.
+narrateur|Une feuille tourne sous la balançoire.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11575,7 +12087,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On range. On met dans la caisse. Inès hoche la tête. On continue, avec papa. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Oui. On met les jouets dans la caisse. Mila hoche la tête. Bravo, Mila. C'est du bon travail. Après le jeu, on range. Dans la caisse. Mila descend de la balançoire. Tu as fini de te balancer ?</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11719,7 +12231,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On range. On met dans la caisse. Inès hoche la tête. On continue, avec papa. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Oui.
+narrateur|On met les jouets dans la caisse.
+narrateur|Mila hoche la tête.
+maman|Bravo, Mila. C'est du bon travail.
+papa|Après le jeu, on range.
+enfant-f|Dans la caisse.
+narrateur|Mila descend de la balançoire.
+maman|Tu as fini de te balancer ?</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11747,7 +12266,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Quel jouet Mila sort, près des balançoires ? Les cubes, le livre, ou la dînette ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11911,7 +12430,8 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Quel jouet Mila sort, près des balançoires ?
+maman|Les cubes, le livre, ou la dînette ?</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11939,7 +12459,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est rouge. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près des balançoires. Une corde de balançoire frotte tout petit. Les cubes sont dans l'herbe, près des balançoires. Les cubes, Mila. Après, dans la caisse. Ils sont un peu mouillés. Mila empile deux cubes. Ça fait clic. Le jeu est fini, tout doux. Elle met les cubes dans la caisse, un par un. Mila pose les pieds bien à plat. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12079,7 +12599,18 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est rouge. On range après le jeu. Papa reste tout près. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près des balançoires.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Les cubes sont dans l'herbe, près des balançoires.
+papa|Les cubes, Mila. Après, dans la caisse.
+enfant-f|Ils sont un peu mouillés.
+narrateur|Mila empile deux cubes. Ça fait clic.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle met les cubes dans la caisse, un par un.
+narrateur|Mila pose les pieds bien à plat.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12107,7 +12638,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12275,7 +12806,9 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12303,7 +12836,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi les balançoires. Puis les cubes. Puis rouge. Un vélo passe au loin. Inès pose sa tête un moment. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti les cubes. Maintenant, la caisse rouge. Le métal du toboggan sèche. Mila voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Elle pousse le couvercle. Toc. Tu as rangé. On peut partir. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12443,7 +12976,19 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Inès a choisi les balançoires. Puis les cubes. Puis rouge. Un vélo passe au loin. Inès pose sa tête un moment. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Le métal du toboggan sèche.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met un cube dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Tu as rangé. On peut partir.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12471,7 +13016,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Un vélo sonne, tout loin. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12611,7 +13156,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Un vélo sonne, tout loin.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12639,7 +13190,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Inès s'arrête près de bleu. les cubes est rangé. On range un objet. Inès montre bleu à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti les cubes. Maintenant, la caisse bleue. La corde de la balançoire ne frotte plus. Mila voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Elle pousse le couvercle. Toc. Le goûter est encore dans le sac. Toc toc, mes chaussures. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12779,10 +13330,26 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Inès s'arrête près de bleu. les cubes est rangé. On range un objet. Inès montre bleu à papa. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse bleue.
+narrateur|La corde de la balançoire ne frotte plus.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met un cube dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Le goûter est encore dans le sac.
+enfant-f|Toc toc, mes chaussures.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12807,7 +13374,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila ajuste son sac. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12947,7 +13514,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila ajuste son sac.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12975,7 +13548,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Inès se souvient de les balançoires. Et de les cubes. Et de vert. On se tient la main. Inès range les balançoires dans sa tête, comme un souvenir. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti les cubes. Maintenant, la caisse verte. Le trottoir mouillé fait des taches claires. Mila voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Elle pousse le couvercle. Toc. Bravo. Les jouets dorment dans la caisse. Le goûter est là. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13115,7 +13688,19 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Inès se souvient de les balançoires. Et de les cubes. Et de vert. On se tient la main. Inès range les balançoires dans sa tête, comme un souvenir. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti les cubes.
+narrateur|Maintenant, la caisse verte.
+narrateur|Le trottoir mouillé fait des taches claires.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met un cube dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Bravo. Les jouets dorment dans la caisse.
+enfant-f|Le goûter est là.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13143,7 +13728,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Papa et maman marchent au même pas. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13283,7 +13868,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Papa et maman marchent au même pas.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13311,7 +13902,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près des balançoires. Une corde de balançoire frotte tout petit. Le livre est sur le banc du square. Le livre, Mila. Après, dans la caisse. Je tourne une page. Mila ouvre le livre. Une image de lune. Le jeu est fini, tout doux. Elle ferme le livre. Elle le pose dans la caisse. Mila pose les pieds bien à plat. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13451,7 +14042,18 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est bleue. On range après le jeu. Papa montre le geste, lentement. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près des balançoires.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Le livre est sur le banc du square.
+maman|Le livre, Mila. Après, dans la caisse.
+enfant-f|Je tourne une page.
+narrateur|Mila ouvre le livre. Une image de lune.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle ferme le livre. Elle le pose dans la caisse.
+narrateur|Mila pose les pieds bien à plat.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13479,7 +14081,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13647,7 +14249,9 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13675,7 +14279,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec rouge. Après le livre. Près de les balançoires. Inès s'arrête. Un crochet tient bien le manteau. Inès raccroche un linge. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti le livre. Maintenant, la caisse rouge. Le moineau s'envole. Mila voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Elle pousse le couvercle. Toc. Tu as fait du bon travail, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13815,7 +14419,19 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec rouge. Après le livre. Près de les balançoires. Inès s'arrête. Un crochet tient bien le manteau. Inès raccroche un linge. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Le moineau s'envole.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met le livre dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Tu as fait du bon travail, Mila.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13843,7 +14459,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le square n'est plus qu'un souvenir de sable. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13983,7 +14599,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le square n'est plus qu'un souvenir de sable.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14011,7 +14633,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Inès range le livre. bleu reste près de les balançoires. On entend un oiseau. Inès caresse le doudou. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti le livre. Maintenant, la caisse bleue. La caisse est lourde d'un cran. Mila voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Elle pousse le couvercle. Toc. On range, puis on marche. C'est ça. C'est calme. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14151,10 +14773,26 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Inès range le livre. bleu reste près de les balançoires. On entend un oiseau. Inès caresse le doudou. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse bleue.
+narrateur|La caisse est lourde d'un cran.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met le livre dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+papa|On range, puis on marche. C'est ça.
+enfant-f|C'est calme.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14179,7 +14817,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a les mains propres, maintenant. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14319,7 +14957,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila a les mains propres, maintenant.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14347,7 +14991,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Vert est là. le livre aussi. les balançoires reste dans le souvenir. On dit merci. J'ai appris. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti le livre. Maintenant, la caisse verte. Le zip du sac est fermé. Mila voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Elle pousse le couvercle. Toc. Le square est vide, tout propre. J'ai mis dedans. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14487,9 +15131,19 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Vert est là. le livre aussi. les balançoires reste dans le souvenir. On dit merci.
-enfant-f|J'ai appris. Après le jeu, on range.
-narrateur|Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti le livre.
+narrateur|Maintenant, la caisse verte.
+narrateur|Le zip du sac est fermé.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met le livre dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+maman|Le square est vide, tout propre.
+enfant-f|J'ai mis dedans.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14517,7 +15171,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'école sent déjà le savon. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14657,7 +15311,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'école sent déjà le savon.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14685,7 +15345,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est verte. On range après le jeu. Je suis là. Après le jeu, on range. Les jouets retournent dans la caisse.</t>
+          <t>Mila est près des balançoires. Une corde de balançoire frotte tout petit. La dînette est dans l'herbe, près de la caisse. La dînette, Mila. Après le jeu, on range. Je sors l'assiette. Mila pose une tasse sur une soucoupe. Ça cliquette. Le jeu est fini, tout doux. Elle range la dînette dans la caisse, tout doux. Mila pose les pieds bien à plat. Bravo. Après le jeu, on range. Les jouets retournent dans la caisse. Dans la caisse.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14825,9 +15485,18 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Inès a sorti la dînette. Elle range. La dînette retourne dans la caisse. La caisse est verte. On range après le jeu.
-papa|Je suis là. Après le jeu, on range.
-narrateur|Les jouets retournent dans la caisse.</t>
+          <t>narrateur|Mila est près des balançoires.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|La dînette est dans l'herbe, près de la caisse.
+papa|La dînette, Mila. Après le jeu, on range.
+enfant-f|Je sors l'assiette.
+narrateur|Mila pose une tasse sur une soucoupe. Ça cliquette.
+narrateur|Le jeu est fini, tout doux.
+narrateur|Elle range la dînette dans la caisse, tout doux.
+narrateur|Mila pose les pieds bien à plat.
+papa|Bravo. Après le jeu, on range.
+maman|Les jouets retournent dans la caisse.
+enfant-f|Dans la caisse.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14855,7 +15524,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15023,7 +15692,9 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+papa|Rouge, bleu, ou vert ?
+maman|Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15051,7 +15722,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Inès essuie ses mains. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti la dînette. Maintenant, la caisse rouge. Une miette de pain reste sur le banc. Mila voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Elle pousse le couvercle. Toc. Merci d'avoir rangé, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15191,7 +15862,19 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Inès rejoint rouge. la dînette est rangé. les balançoires est fini. On attend son tour. Inès essuie ses mains. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse rouge.
+narrateur|Une miette de pain reste sur le banc.
+narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle met la tasse dans la caisse rouge.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Merci d'avoir rangé, Mila.
+enfant-f|La caisse rouge est fermée.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15219,7 +15902,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La rue est calme. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15359,7 +16042,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La rue est calme.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15387,7 +16076,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de bleu. Inès pose la dînette. les balançoires est derrière. Le sol est un peu froid. Inès ferme le sac. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti la dînette. Maintenant, la caisse bleue. Le vent est doux, dans les cheveux. Mila voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Elle pousse le couvercle. Toc. On y va. L'école attend. Oui. C'est rangé. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15527,10 +16216,26 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de bleu. Inès pose la dînette. les balançoires est derrière. Le sol est un peu froid. Inès ferme le sac. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse bleue.
+narrateur|Le vent est doux, dans les cheveux.
+narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle met la tasse dans la caisse bleue.
+narrateur|Elle pousse le couvercle. Toc.
+maman|On y va. L'école attend.
+enfant-f|Oui. C'est rangé.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15555,7 +16260,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila regarde le portail jaune. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15695,7 +16400,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila regarde le portail jaune.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15723,7 +16434,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Inès montre vert. Papa a vu les balançoires. Et la dînette. Un ruban reste dans la poche. Inès tend vert à maman. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>Mila a joué près des balançoires. Elle a sorti la dînette. Maintenant, la caisse verte. L'école n'est plus très loin. Mila voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Elle pousse le couvercle. Toc. Après le jeu, la caisse. Bravo. On y va. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15863,7 +16574,19 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Inès montre vert. Papa a vu les balançoires. Et la dînette. Un ruban reste dans la poche. Inès tend vert à maman. Après le jeu, on range. Les jouets retournent dans la caisse. On met dans la caisse. On range. Inès dit merci à papa.</t>
+          <t>narrateur|Mila a joué près des balançoires.
+narrateur|Elle a sorti la dînette.
+narrateur|Maintenant, la caisse verte.
+narrateur|L'école n'est plus très loin.
+narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle met la tasse dans la caisse verte.
+narrateur|Elle pousse le couvercle. Toc.
+papa|Après le jeu, la caisse. Bravo.
+enfant-f|On y va.
+papa|Après le jeu, on range.
+maman|Les jouets sont dans la caisse.
+enfant-f|C'est rangé.
+narrateur|Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15891,7 +16614,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La caisse reste fermée, jusqu'à l'école. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16031,7 +16754,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La caisse reste fermée, jusqu'à l'école.
+narrateur|Mila a rangé.
+narrateur|Les jouets sont dans la caisse.
+papa|Bravo, Mila.
+maman|Tu as fait du bon travail.
+enfant-f|On va à l'école.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16053,7 +16782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16147,6 +16876,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-004.xlsx
+++ b/stories/arbres/TREE-AUT-004.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le pain chaud sort de la boulangerie. Ça sent la croûte dorée, tout le long de la rue. Une flaque brille comme un petit miroir. Le sac de Mila tape doucement son dos. Toc toc. Un moineau picore une miette. J'ai mis le goûter dans le sac. Tu as tes chaussons de sport, Mila ? Oui, maman. On marche ensemble jusqu'à l'école. Papa tient une petite caisse par la poignée. Des jouets dorment dedans. En ce moment, ils suivent le trottoir mouillé. Juste après le pain, il y a un petit square. Le sable est encore frais. Le toboggan brille. Les balançoires bougent un tout petit peu. On peut jouer un peu, Mila. Après le jeu, les jouets retournent dans la caisse. D'accord, papa.</t>
+          <t>Le pain chaud sort de la boulangerie. Ça sent la croûte dorée, tout le long de la rue. Une flaque brille comme un petit miroir. Le sac de Mila tape doucement son dos. Toc toc. Des feuilles jaunes collent au trottoir. Un moineau picore une miette. La clochette de la boulangerie tinte une fois. J'ai mis le goûter dans le sac. Tu as tes chaussons de sport, Mila ? Oui, maman. On marche ensemble jusqu'à l'école. Papa tient une petite caisse par la poignée. Des jouets dorment dedans. En ce moment, ils suivent le trottoir mouillé. Juste après le pain, il y a un petit square. Le sable est encore frais. Le toboggan brille. Les balançoires bougent un tout petit peu. On peut jouer un peu, Mila. Après le jeu, les jouets retournent dans la caisse. D'accord, papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1342,7 +1342,9 @@
 narrateur|Une flaque brille comme un petit miroir.
 narrateur|Le sac de Mila tape doucement son dos.
 narrateur|Toc toc.
+narrateur|Des feuilles jaunes collent au trottoir.
 narrateur|Un moineau picore une miette.
+narrateur|La clochette de la boulangerie tinte une fois.
 maman|J'ai mis le goûter dans le sac.
 maman|Tu as tes chaussons de sport, Mila ?
 enfant-f|Oui, maman.
@@ -1720,13 +1722,17 @@
         <is>
           <t>narrateur|Mila s'agenouille près du bac à sable.
 narrateur|Le sable est frais, un peu humide.
-narrateur|Il coule entre ses doigts. Chh.
+narrateur|Il coule entre ses doigts.
+narrateur|Chh.
 narrateur|Papa pose la caisse à côté.
-papa|Tu joues un peu. Après, on range.
-enfant-f|Oui. Dans la caisse.
+papa|Tu joues un peu.
+papa|Après, on range.
+enfant-f|Oui.
+enfant-f|Dans la caisse.
 narrateur|Mila fait un petit tas.
 narrateur|Un cube dépasse déjà du sable.
-maman|Bravo, Mila. Le sable reste dans le bac.
+maman|Bravo, Mila.
+maman|Le sable reste dans le bac.
 narrateur|Un oiseau crie au-dessus du square.
 papa|Quand le jeu est fini, les jouets vont dans la caisse.
 enfant-f|Je range après.</t>
@@ -2092,7 +2098,8 @@
           <t>narrateur|Oui.
 narrateur|Mila a joué un peu.
 narrateur|Elle souffle sur ses mains.
-papa|Bravo. Après le jeu, on range.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.
 narrateur|La caisse attend, ouverte.
@@ -2460,13 +2467,18 @@
           <t>narrateur|Mila est près du bac à sable.
 narrateur|Le sable sent la terre fraîche.
 narrateur|Les cubes sont un peu sablés.
-papa|Les cubes, Mila. Après le jeu, dans la caisse.
-enfant-f|Clic. Clic.
-narrateur|Mila empile deux cubes. Ça fait clic.
+papa|Les cubes, Mila.
+papa|Après le jeu, dans la caisse.
+enfant-f|Clic.
+enfant-f|Clic.
+narrateur|Mila empile deux cubes.
+narrateur|Ça fait clic.
 narrateur|Le jeu est fini, tout doux.
 narrateur|Elle met les cubes dans la caisse, un par un.
-narrateur|Mila secoue un peu ses mains. Le sable tombe.
-papa|Bravo. Après le jeu, on range.
+narrateur|Mila secoue un peu ses mains.
+narrateur|Le sable tombe.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -2496,7 +2508,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2664,7 +2676,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -2694,7 +2706,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti les cubes. Maintenant, la caisse rouge. Un moineau reprend sa miette, plus loin. Mila voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Elle pousse le couvercle. Toc. Bravo, Mila. Les jouets sont dans la caisse. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Un moineau reprend sa miette, plus loin. Elle voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. Bravo, Mila. Les jouets sont dans la caisse. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2834,14 +2846,15 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|Un moineau reprend sa miette, plus loin.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met un cube dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Bravo, Mila. Les jouets sont dans la caisse.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Bravo, Mila.
+papa|Les jouets sont dans la caisse.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -2874,7 +2887,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ils reprennent le trottoir mouillé. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Ils reprennent le trottoir mouillé. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Les jouets sont dans la caisse. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3018,7 +3031,7 @@
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
 papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Les jouets sont dans la caisse.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3048,7 +3061,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti les cubes. Maintenant, la caisse bleue. La flaque du trottoir tremble un peu. Mila voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Elle pousse le couvercle. Toc. Tu as rangé. C'est du bon travail. Dans la caisse. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. La flaque du trottoir tremble un peu. Elle voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. Tu as rangé. C'est du bon travail. Dans la caisse. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3188,14 +3201,15 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|La flaque du trottoir tremble un peu.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met un cube dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
-maman|Tu as rangé. C'est du bon travail.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+maman|Tu as rangé.
+maman|C'est du bon travail.
 enfant-f|Dans la caisse.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -3232,7 +3246,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Le pain de la boulangerie sent encore. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le pain de la boulangerie sent encore. Mila a rangé. Les jouets sont dans la caisse. Tu as rangé. C'est du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3375,8 +3389,8 @@
           <t>narrateur|Le pain de la boulangerie sent encore.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Tu as rangé.
+maman|C'est du bon travail.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3406,7 +3420,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti les cubes. Maintenant, la caisse verte. Le pain chaud sent encore, vers la rue. Mila voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Elle pousse le couvercle. Toc. Après le jeu, tu as rangé. Bravo. J'ai fermé le couvercle. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. Le pain chaud sent encore, vers la rue. Elle voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. Après le jeu, tu as rangé. Bravo. J'ai fermé le couvercle. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3546,14 +3560,15 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|Le pain chaud sent encore, vers la rue.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met un cube dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Après le jeu, tu as rangé. Bravo.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Après le jeu, tu as rangé.
+papa|Bravo.
 enfant-f|J'ai fermé le couvercle.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -3586,7 +3601,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'école montre son portail, tout loin. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>L'école montre son portail, tout loin. Mila a rangé. Les jouets sont dans la caisse. Après le jeu, tu as rangé. Bravo. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3729,8 +3744,8 @@
           <t>narrateur|L'école montre son portail, tout loin.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Après le jeu, tu as rangé.
+papa|Bravo.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -3903,13 +3918,18 @@
           <t>narrateur|Mila est près du bac à sable.
 narrateur|Le sable sent la terre fraîche.
 narrateur|Le livre a un grain de sable sur la couverture.
-maman|Le livre, Mila. Après, il va dans la caisse.
+maman|Le livre, Mila.
+maman|Après, il va dans la caisse.
 enfant-f|Je l'essuie un peu.
-narrateur|Mila ouvre le livre. Une image de lune.
+narrateur|Mila ouvre le livre.
+narrateur|Une image de lune.
 narrateur|Le jeu est fini, tout doux.
-narrateur|Elle ferme le livre. Elle le pose dans la caisse.
-narrateur|Mila secoue un peu ses mains. Le sable tombe.
-papa|Bravo. Après le jeu, on range.
+narrateur|Elle ferme le livre.
+narrateur|Elle le pose dans la caisse.
+narrateur|Mila secoue un peu ses mains.
+narrateur|Le sable tombe.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -3939,7 +3959,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4107,7 +4127,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -4137,7 +4157,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti le livre. Maintenant, la caisse rouge. Un vélo passe. La cloche tinte une fois. Mila voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Elle pousse le couvercle. Toc. La caisse est fermée. Merci, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Un vélo passe. La cloche tinte une fois. Elle voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. La caisse est fermée. Merci, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4277,14 +4297,16 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse rouge.
-narrateur|Un vélo passe. La cloche tinte une fois.
-narrateur|Mila voit une feuille rouge près du pied.
+          <t>narrateur|Mila ouvre la caisse rouge.
+narrateur|Un vélo passe.
+narrateur|La cloche tinte une fois.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met le livre dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
-maman|La caisse est fermée. Merci, Mila.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+maman|La caisse est fermée.
+maman|Merci, Mila.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -4317,7 +4339,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>La caisse tape un peu la jambe de papa. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>La caisse tape un peu la jambe de papa. Mila a rangé. Les jouets sont dans la caisse. La caisse est fermée. Merci, Mila. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4460,8 +4482,8 @@
           <t>narrateur|La caisse tape un peu la jambe de papa.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|La caisse est fermée.
+maman|Merci, Mila.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -4491,7 +4513,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti le livre. Maintenant, la caisse bleue. Le sac de Mila tape son dos. Toc. Mila voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Elle pousse le couvercle. Toc. On peut marcher. La caisse vient avec nous. Merci, papa. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. Le sac de Mila tape son dos. Toc. Elle voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. On peut marcher. La caisse vient avec nous. Merci, papa. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4631,14 +4653,16 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse bleue.
-narrateur|Le sac de Mila tape son dos. Toc.
-narrateur|Mila voit un galet bleu près du pied.
+          <t>narrateur|Mila ouvre la caisse bleue.
+narrateur|Le sac de Mila tape son dos.
+narrateur|Toc.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met le livre dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
-papa|On peut marcher. La caisse vient avec nous.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|On peut marcher.
+papa|La caisse vient avec nous.
 enfant-f|Merci, papa.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -4675,7 +4699,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Mila marche sur les dalles, une par une. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Mila marche sur les dalles, une par une. Mila a rangé. Les jouets sont dans la caisse. On peut marcher. La caisse vient avec nous. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4818,8 +4842,8 @@
           <t>narrateur|Mila marche sur les dalles, une par une.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|On peut marcher.
+papa|La caisse vient avec nous.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -4849,7 +4873,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti le livre. Maintenant, la caisse verte. Le couvercle de la caisse attend. Mila voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Elle pousse le couvercle. Toc. Tu as mis les jouets dans la caisse. Merci, maman. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. Le couvercle de la caisse attend. Elle voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. Tu as mis les jouets dans la caisse. Merci, maman. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4989,13 +5013,13 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|Le couvercle de la caisse attend.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met le livre dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 maman|Tu as mis les jouets dans la caisse.
 enfant-f|Merci, maman.
 papa|Après le jeu, on range.
@@ -5029,7 +5053,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Une flaque reflète le sac. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Une flaque reflète le sac. Mila a rangé. Les jouets sont dans la caisse. Tu as mis les jouets dans la caisse. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5172,8 +5196,7 @@
           <t>narrateur|Une flaque reflète le sac.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Tu as mis les jouets dans la caisse.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -5346,13 +5369,17 @@
           <t>narrateur|Mila est près du bac à sable.
 narrateur|Le sable sent la terre fraîche.
 narrateur|La dînette est froide, posée sur le bois du bac.
-papa|La dînette, Mila. Après, dans la caisse.
+papa|La dînette, Mila.
+papa|Après, dans la caisse.
 enfant-f|La tasse est petite.
-narrateur|Mila pose une tasse sur une soucoupe. Ça cliquette.
+narrateur|Mila pose une tasse sur une soucoupe.
+narrateur|Ça cliquette.
 narrateur|Le jeu est fini, tout doux.
 narrateur|Elle range la dînette dans la caisse, tout doux.
-narrateur|Mila secoue un peu ses mains. Le sable tombe.
-papa|Bravo. Après le jeu, on range.
+narrateur|Mila secoue un peu ses mains.
+narrateur|Le sable tombe.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -5382,7 +5409,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5550,7 +5577,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -5580,7 +5607,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti la dînette. Maintenant, la caisse rouge. Une feuille tourne dans le bac. Mila voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Elle pousse le couvercle. Toc. Bravo. Le square est calme. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Une feuille tourne dans le bac. Elle voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. Bravo. Le square est calme. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5720,14 +5747,15 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|Une feuille tourne dans le bac.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met la tasse dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Bravo. Le square est calme.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Bravo.
+papa|Le square est calme.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -5760,7 +5788,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Le moineau n'est plus là. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le moineau n'est plus là. Mila a rangé. Les jouets sont dans la caisse. Bravo. Le square est calme. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5903,8 +5931,8 @@
           <t>narrateur|Le moineau n'est plus là.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Bravo.
+papa|Le square est calme.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -5934,7 +5962,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti la dînette. Maintenant, la caisse bleue. Le toboggan ne brille plus autant. Mila voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Elle pousse le couvercle. Toc. Tu as fini de ranger tes jouets ? Le livre est dedans. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. Le toboggan ne brille plus autant. Elle voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. Tu as fini de ranger tes jouets ? Le livre est dedans. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6074,13 +6102,13 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|Le toboggan ne brille plus autant.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met la tasse dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 maman|Tu as fini de ranger tes jouets ?
 enfant-f|Le livre est dedans.
 papa|Après le jeu, on range.
@@ -6118,7 +6146,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Le square reste derrière, calme. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le square reste derrière, calme. Mila a rangé. Les jouets sont dans la caisse. Tu as fini de ranger tes jouets ? On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6261,8 +6289,7 @@
           <t>narrateur|Le square reste derrière, calme.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Tu as fini de ranger tes jouets ?
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -6292,7 +6319,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du bac à sable. Elle a sorti la dînette. Maintenant, la caisse verte. La balançoire s'arrête, tout à fait. Mila voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Elle pousse le couvercle. Toc. Oui. C'est rangé. On y va. La tasse aussi. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. La balançoire s'arrête, tout à fait. Elle voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Le sable sent la terre fraîche. Elle pousse le couvercle. Toc. Oui. C'est rangé. On y va. La tasse aussi. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6432,14 +6459,16 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du bac à sable.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|La balançoire s'arrête, tout à fait.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met la tasse dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Oui. C'est rangé. On y va.
+narrateur|Le sable sent la terre fraîche.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Oui.
+papa|C'est rangé.
+papa|On y va.
 enfant-f|La tasse aussi.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -6472,7 +6501,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le goûter fait un petit bruit. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le goûter fait un petit bruit. Mila a rangé. Les jouets sont dans la caisse. Oui. C'est rangé. On y va. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6615,8 +6644,9 @@
           <t>narrateur|Le goûter fait un petit bruit.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Oui.
+papa|C'est rangé.
+papa|On y va.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -6788,11 +6818,14 @@
         <is>
           <t>narrateur|Mila monte les deux marches du toboggan.
 narrateur|Le métal est frais sous ses mains.
-narrateur|Elle glisse une fois. Wouh.
+narrateur|Elle glisse une fois.
+narrateur|Wouh.
 narrateur|Ses pieds retrouvent le tapis souple.
-papa|Une fois, Mila. Puis on range.
+papa|Une fois, Mila.
+papa|Puis on range.
 enfant-f|Encore les pieds par terre.
-maman|Bravo. Tu es descendue doucement.
+maman|Bravo.
+maman|Tu es descendue doucement.
 narrateur|Papa garde la caisse près du pied du toboggan.
 narrateur|Un jouet dépasse déjà.
 papa|Après le jeu, les jouets retournent dans la caisse.
@@ -7163,7 +7196,8 @@
           <t>narrateur|Oui.
 narrateur|Les jouets vont dans la caisse.
 narrateur|Mila le répète tout bas.
-papa|Bravo. Dans la caisse.
+papa|Bravo.
+papa|Dans la caisse.
 maman|Après le jeu, on range.
 enfant-f|Dans la caisse, maman.
 narrateur|Mila essuie ses mains sur son manteau.
@@ -7531,13 +7565,16 @@
           <t>narrateur|Mila est près du toboggan.
 narrateur|Le métal du toboggan est encore frais.
 narrateur|Les cubes attendent au pied du toboggan.
-maman|Les cubes, Mila. Puis on range dans la caisse.
+maman|Les cubes, Mila.
+maman|Puis on range dans la caisse.
 enfant-f|Je fais une tour basse.
-narrateur|Mila empile deux cubes. Ça fait clic.
+narrateur|Mila empile deux cubes.
+narrateur|Ça fait clic.
 narrateur|Le jeu est fini, tout doux.
 narrateur|Elle met les cubes dans la caisse, un par un.
 narrateur|Mila pose un pied sur le tapis souple.
-papa|Bravo. Après le jeu, on range.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -7567,7 +7604,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7735,7 +7772,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -7765,7 +7802,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti les cubes. Maintenant, la caisse rouge. Le goûter fait un petit bruit dans le sac. Mila voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Elle pousse le couvercle. Toc. Bravo, Mila. C'est du bon travail. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Le goûter fait un petit bruit dans le sac. Elle voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. Bravo, Mila. C'est du bon travail. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7905,14 +7942,15 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|Le goûter fait un petit bruit dans le sac.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met un cube dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
-maman|Bravo, Mila. C'est du bon travail.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -7945,7 +7983,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Mila serre la main de maman. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Mila serre la main de maman. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. C'est du bon travail. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -8088,8 +8126,8 @@
           <t>narrateur|Mila serre la main de maman.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8119,7 +8157,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti les cubes. Maintenant, la caisse bleue. Un galet est encore chaud de soleil. Mila voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Elle pousse le couvercle. Toc. Les cubes sont dans la caisse. C'est lourd un peu. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. Un galet est encore chaud de soleil. Elle voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. Les cubes sont dans la caisse. C'est lourd un peu. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -8259,13 +8297,13 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|Un galet est encore chaud de soleil.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met un cube dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 papa|Les cubes sont dans la caisse.
 enfant-f|C'est lourd un peu.
 papa|Après le jeu, on range.
@@ -8303,7 +8341,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Papa change d'épaule, pour la caisse. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Papa change d'épaule, pour la caisse. Mila a rangé. Les jouets sont dans la caisse. Les cubes sont dans la caisse. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8446,8 +8484,7 @@
           <t>narrateur|Papa change d'épaule, pour la caisse.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Les cubes sont dans la caisse.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8477,7 +8514,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti les cubes. Maintenant, la caisse verte. L'herbe colle un peu aux chaussures. Mila voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Elle pousse le couvercle. Toc. Le livre est à sa place, dans la caisse. On va à l'école. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. L'herbe colle un peu aux chaussures. Elle voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. Le livre est à sa place, dans la caisse. On va à l'école. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8617,13 +8654,13 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|L'herbe colle un peu aux chaussures.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met un cube dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 maman|Le livre est à sa place, dans la caisse.
 enfant-f|On va à l'école.
 papa|Après le jeu, on range.
@@ -8657,7 +8694,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Une cloche tinte, plus près. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Une cloche tinte, plus près. Mila a rangé. Les jouets sont dans la caisse. Le livre est à sa place, dans la caisse. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8800,8 +8837,7 @@
           <t>narrateur|Une cloche tinte, plus près.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Le livre est à sa place, dans la caisse.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -8974,13 +9010,17 @@
           <t>narrateur|Mila est près du toboggan.
 narrateur|Le métal du toboggan est encore frais.
 narrateur|Le livre est dans le sac, tout près.
-papa|Le livre, Mila. Après, il retourne dans la caisse.
+papa|Le livre, Mila.
+papa|Après, il retourne dans la caisse.
 enfant-f|Je regarde une page.
-narrateur|Mila ouvre le livre. Une image de lune.
+narrateur|Mila ouvre le livre.
+narrateur|Une image de lune.
 narrateur|Le jeu est fini, tout doux.
-narrateur|Elle ferme le livre. Elle le pose dans la caisse.
+narrateur|Elle ferme le livre.
+narrateur|Elle le pose dans la caisse.
 narrateur|Mila pose un pied sur le tapis souple.
-papa|Bravo. Après le jeu, on range.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -9010,7 +9050,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -9178,7 +9218,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -9208,7 +9248,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti le livre. Maintenant, la caisse rouge. La poignée de la caisse est lisse. Mila voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Elle pousse le couvercle. Toc. La dînette ne cliquette plus. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. La poignée de la caisse est lisse. Elle voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. La dînette ne cliquette plus. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9348,13 +9388,13 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|La poignée de la caisse est lisse.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met le livre dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 papa|La dînette ne cliquette plus.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
@@ -9388,7 +9428,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures de Mila font toc toc. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Les chaussures de Mila font toc toc. Mila a rangé. Les jouets sont dans la caisse. La dînette ne cliquette plus. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9531,8 +9571,7 @@
           <t>narrateur|Les chaussures de Mila font toc toc.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|La dînette ne cliquette plus.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -9562,7 +9601,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti le livre. Maintenant, la caisse bleue. Maman ajuste l'écharpe de Mila. Mila voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Elle pousse le couvercle. Toc. Après le jeu, on range. Tu l'as fait. Le sable est resté. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. Maman ajuste l'écharpe de Mila. Elle voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. Après le jeu, on range. Tu l'as fait. Le sable est resté. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9702,14 +9741,15 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|Maman ajuste l'écharpe de Mila.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met le livre dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
-maman|Après le jeu, on range. Tu l'as fait.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+maman|Après le jeu, on range.
+maman|Tu l'as fait.
 enfant-f|Le sable est resté.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -9746,7 +9786,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le vent pousse une feuille sèche. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le vent pousse une feuille sèche. Mila a rangé. Les jouets sont dans la caisse. Après le jeu, on range. Tu l'as fait. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9889,8 +9929,8 @@
           <t>narrateur|Le vent pousse une feuille sèche.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Après le jeu, on range.
+maman|Tu l'as fait.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -9920,7 +9960,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti le livre. Maintenant, la caisse verte. Papa souffle dans ses mains. Mila voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Elle pousse le couvercle. Toc. Merci, Mila. On reprend le chemin. C'est fini, le jeu. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. Papa souffle dans ses mains. Elle voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. Merci, Mila. On reprend le chemin. C'est fini, le jeu. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -10060,14 +10100,15 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|Papa souffle dans ses mains.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met le livre dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Merci, Mila. On reprend le chemin.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Merci, Mila.
+papa|On reprend le chemin.
 enfant-f|C'est fini, le jeu.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -10100,7 +10141,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Le portail de l'école est jaune. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le portail de l'école est jaune. Mila a rangé. Les jouets sont dans la caisse. Merci, Mila. On reprend le chemin. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -10243,8 +10284,8 @@
           <t>narrateur|Le portail de l'école est jaune.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Merci, Mila.
+papa|On reprend le chemin.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -10417,13 +10458,16 @@
           <t>narrateur|Mila est près du toboggan.
 narrateur|Le métal du toboggan est encore frais.
 narrateur|La dînette est dans la caisse, déjà à moitié.
-maman|La dînette, Mila. Après le jeu, on range.
+maman|La dînette, Mila.
+maman|Après le jeu, on range.
 enfant-f|Je sors la tasse.
-narrateur|Mila pose une tasse sur une soucoupe. Ça cliquette.
+narrateur|Mila pose une tasse sur une soucoupe.
+narrateur|Ça cliquette.
 narrateur|Le jeu est fini, tout doux.
 narrateur|Elle range la dînette dans la caisse, tout doux.
 narrateur|Mila pose un pied sur le tapis souple.
-papa|Bravo. Après le jeu, on range.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -10453,7 +10497,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10621,7 +10665,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -10651,7 +10695,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti la dînette. Maintenant, la caisse rouge. Le square redevient calme. Mila voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Elle pousse le couvercle. Toc. Tu tiens bien le couvercle. Bravo. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Le square redevient calme. Elle voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. Tu tiens bien le couvercle. Bravo. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10791,14 +10835,15 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|Le square redevient calme.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met la tasse dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
-maman|Tu tiens bien le couvercle. Bravo.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+maman|Tu tiens bien le couvercle.
+maman|Bravo.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -10831,7 +10876,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Mila sent le pain, une dernière fois. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Mila sent le pain, une dernière fois. Mila a rangé. Les jouets sont dans la caisse. Tu tiens bien le couvercle. Bravo. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10974,8 +11019,8 @@
           <t>narrateur|Mila sent le pain, une dernière fois.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Tu tiens bien le couvercle.
+maman|Bravo.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11005,7 +11050,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti la dînette. Maintenant, la caisse bleue. Une cloche d'école tinte, tout loin. Mila voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Elle pousse le couvercle. Toc. La caisse est prête. Bravo. La caisse est bleue. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. Une cloche d'école tinte, tout loin. Elle voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. La caisse est prête. Bravo. La caisse est bleue. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11145,14 +11190,15 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|Une cloche d'école tinte, tout loin.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met la tasse dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
-papa|La caisse est prête. Bravo.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|La caisse est prête.
+papa|Bravo.
 enfant-f|La caisse est bleue.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -11189,7 +11235,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>La caisse ne s'ouvre plus. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>La caisse ne s'ouvre plus. Mila a rangé. Les jouets sont dans la caisse. La caisse est prête. Bravo. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11332,8 +11378,8 @@
           <t>narrateur|La caisse ne s'ouvre plus.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|La caisse est prête.
+papa|Bravo.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11363,7 +11409,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près du toboggan. Elle a sorti la dînette. Maintenant, la caisse verte. Le sable ne coule plus. Mila voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Elle pousse le couvercle. Toc. On marche jusqu'à l'école. La caisse est verte. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. Le sable ne coule plus. Elle voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Le métal du toboggan est encore frais. Elle pousse le couvercle. Toc. On marche jusqu'à l'école. La caisse est verte. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11503,13 +11549,13 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près du toboggan.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|Le sable ne coule plus.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met la tasse dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Le métal du toboggan est encore frais.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 maman|On marche jusqu'à l'école.
 enfant-f|La caisse est verte.
 papa|Après le jeu, on range.
@@ -11543,7 +11589,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Le trottoir sèche par plaques. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le trottoir sèche par plaques. Mila a rangé. Les jouets sont dans la caisse. On marche jusqu'à l'école. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11686,8 +11732,7 @@
           <t>narrateur|Le trottoir sèche par plaques.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|On marche jusqu'à l'école.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -11860,9 +11905,11 @@
           <t>narrateur|Mila s'assoit sur une balançoire.
 narrateur|Le siège est un peu froid.
 narrateur|Elle avance tout doux, puis s'arrête.
-maman|Un petit moment, Mila. Puis on range.
+maman|Un petit moment, Mila.
+maman|Puis on range.
 enfant-f|Je me tiens bien.
-papa|Bravo. Tes mains tiennent la corde.
+papa|Bravo.
+papa|Tes mains tiennent la corde.
 narrateur|La caisse est posée dans l'herbe.
 narrateur|Un couvercle attend, ouvert.
 maman|Après le jeu, les jouets retournent dans la caisse.
@@ -12234,7 +12281,8 @@
           <t>narrateur|Oui.
 narrateur|On met les jouets dans la caisse.
 narrateur|Mila hoche la tête.
-maman|Bravo, Mila. C'est du bon travail.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
 papa|Après le jeu, on range.
 enfant-f|Dans la caisse.
 narrateur|Mila descend de la balançoire.
@@ -12602,13 +12650,16 @@
           <t>narrateur|Mila est près des balançoires.
 narrateur|Une corde de balançoire frotte tout petit.
 narrateur|Les cubes sont dans l'herbe, près des balançoires.
-papa|Les cubes, Mila. Après, dans la caisse.
+papa|Les cubes, Mila.
+papa|Après, dans la caisse.
 enfant-f|Ils sont un peu mouillés.
-narrateur|Mila empile deux cubes. Ça fait clic.
+narrateur|Mila empile deux cubes.
+narrateur|Ça fait clic.
 narrateur|Le jeu est fini, tout doux.
 narrateur|Elle met les cubes dans la caisse, un par un.
 narrateur|Mila pose les pieds bien à plat.
-papa|Bravo. Après le jeu, on range.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -12638,7 +12689,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12806,7 +12857,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -12836,7 +12887,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti les cubes. Maintenant, la caisse rouge. Le métal du toboggan sèche. Mila voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Elle pousse le couvercle. Toc. Tu as rangé. On peut partir. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Le métal du toboggan sèche. Elle voit une feuille rouge près du pied. Elle met un cube dans la caisse rouge. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. Tu as rangé. On peut partir. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12976,14 +13027,15 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|Le métal du toboggan sèche.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met un cube dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Tu as rangé. On peut partir.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Tu as rangé.
+papa|On peut partir.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -13016,7 +13068,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Un vélo sonne, tout loin. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Un vélo sonne, tout loin. Mila a rangé. Les jouets sont dans la caisse. Tu as rangé. On peut partir. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13159,8 +13211,8 @@
           <t>narrateur|Un vélo sonne, tout loin.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Tu as rangé.
+papa|On peut partir.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -13190,7 +13242,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti les cubes. Maintenant, la caisse bleue. La corde de la balançoire ne frotte plus. Mila voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Elle pousse le couvercle. Toc. Le goûter est encore dans le sac. Toc toc, mes chaussures. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. La corde de la balançoire ne frotte plus. Elle voit un galet bleu près du pied. Elle met un cube dans la caisse bleue. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. Le goûter est encore dans le sac. Toc toc, mes chaussures. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -13330,13 +13382,13 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|La corde de la balançoire ne frotte plus.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met un cube dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 maman|Le goûter est encore dans le sac.
 enfant-f|Toc toc, mes chaussures.
 papa|Après le jeu, on range.
@@ -13374,7 +13426,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Mila ajuste son sac. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Mila ajuste son sac. Mila a rangé. Les jouets sont dans la caisse. Le goûter est encore dans le sac. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13517,8 +13569,7 @@
           <t>narrateur|Mila ajuste son sac.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Le goûter est encore dans le sac.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -13548,7 +13599,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti les cubes. Maintenant, la caisse verte. Le trottoir mouillé fait des taches claires. Mila voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Elle pousse le couvercle. Toc. Bravo. Les jouets dorment dans la caisse. Le goûter est là. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. Le trottoir mouillé fait des taches claires. Elle voit une feuille verte près du pied. Elle met un cube dans la caisse verte. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. Bravo. Les jouets dorment dans la caisse. Le goûter est là. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13688,14 +13739,15 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti les cubes.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|Le trottoir mouillé fait des taches claires.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met un cube dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Bravo. Les jouets dorment dans la caisse.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Bravo.
+papa|Les jouets dorment dans la caisse.
 enfant-f|Le goûter est là.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -13728,7 +13780,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Papa et maman marchent au même pas. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Papa et maman marchent au même pas. Mila a rangé. Les jouets sont dans la caisse. Bravo. Les jouets dorment dans la caisse. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13871,8 +13923,8 @@
           <t>narrateur|Papa et maman marchent au même pas.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Bravo.
+papa|Les jouets dorment dans la caisse.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14045,13 +14097,17 @@
           <t>narrateur|Mila est près des balançoires.
 narrateur|Une corde de balançoire frotte tout petit.
 narrateur|Le livre est sur le banc du square.
-maman|Le livre, Mila. Après, dans la caisse.
+maman|Le livre, Mila.
+maman|Après, dans la caisse.
 enfant-f|Je tourne une page.
-narrateur|Mila ouvre le livre. Une image de lune.
+narrateur|Mila ouvre le livre.
+narrateur|Une image de lune.
 narrateur|Le jeu est fini, tout doux.
-narrateur|Elle ferme le livre. Elle le pose dans la caisse.
+narrateur|Elle ferme le livre.
+narrateur|Elle le pose dans la caisse.
 narrateur|Mila pose les pieds bien à plat.
-papa|Bravo. Après le jeu, on range.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -14081,7 +14137,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -14249,7 +14305,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -14279,7 +14335,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti le livre. Maintenant, la caisse rouge. Le moineau s'envole. Mila voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Elle pousse le couvercle. Toc. Tu as fait du bon travail, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Le moineau s'envole. Elle voit une feuille rouge près du pied. Elle met le livre dans la caisse rouge. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. Tu as fait du bon travail, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14419,13 +14475,13 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|Le moineau s'envole.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met le livre dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 maman|Tu as fait du bon travail, Mila.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
@@ -14459,7 +14515,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Le square n'est plus qu'un souvenir de sable. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Le square n'est plus qu'un souvenir de sable. Mila a rangé. Les jouets sont dans la caisse. Tu as fait du bon travail, Mila. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14602,8 +14658,7 @@
           <t>narrateur|Le square n'est plus qu'un souvenir de sable.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Tu as fait du bon travail, Mila.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14633,7 +14688,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti le livre. Maintenant, la caisse bleue. La caisse est lourde d'un cran. Mila voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Elle pousse le couvercle. Toc. On range, puis on marche. C'est ça. C'est calme. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. La caisse est lourde d'un cran. Elle voit un galet bleu près du pied. Elle met le livre dans la caisse bleue. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. On range, puis on marche. C'est ça. C'est calme. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14773,14 +14828,15 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|La caisse est lourde d'un cran.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met le livre dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
-papa|On range, puis on marche. C'est ça.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|On range, puis on marche.
+papa|C'est ça.
 enfant-f|C'est calme.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -14817,7 +14873,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Mila a les mains propres, maintenant. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Mila a les mains propres, maintenant. Mila a rangé. Les jouets sont dans la caisse. On range, puis on marche. C'est ça. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14960,8 +15016,8 @@
           <t>narrateur|Mila a les mains propres, maintenant.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|On range, puis on marche.
+papa|C'est ça.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -14991,7 +15047,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti le livre. Maintenant, la caisse verte. Le zip du sac est fermé. Mila voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Elle pousse le couvercle. Toc. Le square est vide, tout propre. J'ai mis dedans. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. Le zip du sac est fermé. Elle voit une feuille verte près du pied. Elle met le livre dans la caisse verte. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. Le square est vide, tout propre. J'ai mis dedans. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -15131,13 +15187,13 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti le livre.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|Le zip du sac est fermé.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met le livre dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 maman|Le square est vide, tout propre.
 enfant-f|J'ai mis dedans.
 papa|Après le jeu, on range.
@@ -15171,7 +15227,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'école sent déjà le savon. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>L'école sent déjà le savon. Mila a rangé. Les jouets sont dans la caisse. Le square est vide, tout propre. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -15314,8 +15370,7 @@
           <t>narrateur|L'école sent déjà le savon.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|Le square est vide, tout propre.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -15488,13 +15543,16 @@
           <t>narrateur|Mila est près des balançoires.
 narrateur|Une corde de balançoire frotte tout petit.
 narrateur|La dînette est dans l'herbe, près de la caisse.
-papa|La dînette, Mila. Après le jeu, on range.
+papa|La dînette, Mila.
+papa|Après le jeu, on range.
 enfant-f|Je sors l'assiette.
-narrateur|Mila pose une tasse sur une soucoupe. Ça cliquette.
+narrateur|Mila pose une tasse sur une soucoupe.
+narrateur|Ça cliquette.
 narrateur|Le jeu est fini, tout doux.
 narrateur|Elle range la dînette dans la caisse, tout doux.
 narrateur|Mila pose les pieds bien à plat.
-papa|Bravo. Après le jeu, on range.
+papa|Bravo.
+papa|Après le jeu, on range.
 maman|Les jouets retournent dans la caisse.
 enfant-f|Dans la caisse.</t>
         </is>
@@ -15524,7 +15582,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Quelle caisse Mila ferme-t-elle ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
+          <t>Mila prend quelle caisse ? Rouge, bleu, ou vert ? Tu choisis la couleur.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15692,7 +15750,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|Quelle caisse Mila ferme-t-elle ?
+          <t>narrateur|Mila prend quelle caisse ?
 papa|Rouge, bleu, ou vert ?
 maman|Tu choisis la couleur.</t>
         </is>
@@ -15722,7 +15780,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti la dînette. Maintenant, la caisse rouge. Une miette de pain reste sur le banc. Mila voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Elle pousse le couvercle. Toc. Merci d'avoir rangé, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse rouge. Une miette de pain reste sur le banc. Elle voit une feuille rouge près du pied. Elle met la tasse dans la caisse rouge. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. Merci d'avoir rangé, Mila. La caisse rouge est fermée. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15862,13 +15920,13 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse rouge.
+          <t>narrateur|Mila ouvre la caisse rouge.
 narrateur|Une miette de pain reste sur le banc.
-narrateur|Mila voit une feuille rouge près du pied.
+narrateur|Elle voit une feuille rouge près du pied.
 narrateur|Elle met la tasse dans la caisse rouge.
-narrateur|Elle pousse le couvercle. Toc.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
 papa|Merci d'avoir rangé, Mila.
 enfant-f|La caisse rouge est fermée.
 papa|Après le jeu, on range.
@@ -15902,7 +15960,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>La rue est calme. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>La rue est calme. Mila a rangé. Les jouets sont dans la caisse. Merci d'avoir rangé, Mila. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -16045,8 +16103,7 @@
           <t>narrateur|La rue est calme.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Merci d'avoir rangé, Mila.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16076,7 +16133,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti la dînette. Maintenant, la caisse bleue. Le vent est doux, dans les cheveux. Mila voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Elle pousse le couvercle. Toc. On y va. L'école attend. Oui. C'est rangé. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse bleue. Le vent est doux, dans les cheveux. Elle voit un galet bleu près du pied. Elle met la tasse dans la caisse bleue. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. On y va. L'école attend. Oui. C'est rangé. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -16216,15 +16273,17 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse bleue.
+          <t>narrateur|Mila ouvre la caisse bleue.
 narrateur|Le vent est doux, dans les cheveux.
-narrateur|Mila voit un galet bleu près du pied.
+narrateur|Elle voit un galet bleu près du pied.
 narrateur|Elle met la tasse dans la caisse bleue.
-narrateur|Elle pousse le couvercle. Toc.
-maman|On y va. L'école attend.
-enfant-f|Oui. C'est rangé.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+maman|On y va.
+maman|L'école attend.
+enfant-f|Oui.
+enfant-f|C'est rangé.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
 enfant-f|C'est rangé.
@@ -16260,7 +16319,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Mila regarde le portail jaune. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>Mila regarde le portail jaune. Mila a rangé. Les jouets sont dans la caisse. On y va. L'école attend. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16403,8 +16462,8 @@
           <t>narrateur|Mila regarde le portail jaune.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+maman|On y va.
+maman|L'école attend.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16434,7 +16493,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Mila a joué près des balançoires. Elle a sorti la dînette. Maintenant, la caisse verte. L'école n'est plus très loin. Mila voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Elle pousse le couvercle. Toc. Après le jeu, la caisse. Bravo. On y va. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
+          <t>Mila ouvre la caisse verte. L'école n'est plus très loin. Elle voit une feuille verte près du pied. Elle met la tasse dans la caisse verte. Une corde de balançoire frotte tout petit. Elle pousse le couvercle. Toc. Après le jeu, la caisse. Bravo. On y va. Après le jeu, on range. Les jouets sont dans la caisse. C'est rangé. Ils reprennent le chemin de l'école.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -16574,14 +16633,15 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Mila a joué près des balançoires.
-narrateur|Elle a sorti la dînette.
-narrateur|Maintenant, la caisse verte.
+          <t>narrateur|Mila ouvre la caisse verte.
 narrateur|L'école n'est plus très loin.
-narrateur|Mila voit une feuille verte près du pied.
+narrateur|Elle voit une feuille verte près du pied.
 narrateur|Elle met la tasse dans la caisse verte.
-narrateur|Elle pousse le couvercle. Toc.
-papa|Après le jeu, la caisse. Bravo.
+narrateur|Une corde de balançoire frotte tout petit.
+narrateur|Elle pousse le couvercle.
+narrateur|Toc.
+papa|Après le jeu, la caisse.
+papa|Bravo.
 enfant-f|On y va.
 papa|Après le jeu, on range.
 maman|Les jouets sont dans la caisse.
@@ -16614,7 +16674,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>La caisse reste fermée, jusqu'à l'école. Mila a rangé. Les jouets sont dans la caisse. Bravo, Mila. Tu as fait du bon travail. On va à l'école. L'histoire est finie.</t>
+          <t>La caisse reste fermée, jusqu'à l'école. Mila a rangé. Les jouets sont dans la caisse. Après le jeu, la caisse. Bravo. On va à l'école. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16757,8 +16817,8 @@
           <t>narrateur|La caisse reste fermée, jusqu'à l'école.
 narrateur|Mila a rangé.
 narrateur|Les jouets sont dans la caisse.
-papa|Bravo, Mila.
-maman|Tu as fait du bon travail.
+papa|Après le jeu, la caisse.
+papa|Bravo.
 enfant-f|On va à l'école.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -16782,7 +16842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16881,6 +16941,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
